--- a/github_projects.xlsx
+++ b/github_projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="开源项目汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,10 +98,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,9 +112,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -476,17 +488,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,15 +533,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>简介</t>
+          <t>实用度</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>复现难度</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>最后更新</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>项目简介</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>推荐理由/用途</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -544,6 +580,10 @@
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -560,24 +600,44 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>143167</v>
+        <v>143185</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>The agent engineering platform.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>AI应用生态最广的框架, 学Agent开发首选, 文档全</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -594,24 +654,44 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>69610</v>
+        <v>69617</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>🌟 The Multi-Agent Framework: First AI Software Company, Towards Natural Language Programming</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>多智能体"软件公司", 概念先进但重, 适合进阶</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -628,24 +708,44 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>60152</v>
+        <v>60157</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>A programming framework for agentic AI</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>微软多Agent框架, 企业级, 学习成本较高</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -662,24 +762,44 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>56467</v>
+        <v>56475</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Framework for orchestrating role-playing, autonomous AI agents. By fostering collaborative intellige</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Framework for orchestrating role-playing, autonomous AI agents. By fostering collaborative intelligence, CrewAI empowers agents to work together seaml</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>角色扮演多Agent, 上手快, 中文资料多</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -696,24 +816,44 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>46499</v>
+        <v>46502</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Ultra-lightweight, open-source, self-hosted personal AI agent framework in Python with WebUI, tools,</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Ultra-lightweight, open-source, self-hosted personal AI agent framework in Python with WebUI, tools, memory, MCP, multi-agent workflows, automation, a</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>轻量个人AI助手, 自托管, 适合入门部署</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -730,24 +870,44 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>38630</v>
+        <v>38643</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Build resilient agents.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>状态机式Agent编排, 生产级选择, 需先学LangChain</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -764,24 +924,44 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>38437</v>
+        <v>38438</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent Assistant &amp; development framework that integrates lots of IM platforms, LLMs, plugins and A</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>AI Agent Assistant &amp; development framework that integrates lots of IM platforms, LLMs, plugins and AI feature, and can be your openclaw alternative. ✨</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Agent开发方向, 与你的AI工具链经验契合</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -798,24 +978,44 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>28327</v>
+        <v>28331</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>A lightweight, powerful framework for multi-agent workflows</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Agent开发方向, 与你的AI工具链经验契合</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -830,6 +1030,10 @@
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -853,17 +1057,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Accelerate local LLM inference and finetuning (LLaMA, Mistral, ChatGLM, Qwen, DeepSeek, Mixtral, Gem</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Accelerate local LLM inference and finetuning (LLaMA, Mistral, ChatGLM, Qwen, DeepSeek, Mixtral, Gemma, Phi, MiniCPM, Qwen-VL, MiniCPM-V, etc.) on Int</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Intel官方加速本地LLM, 你的i7-1260P是Intel, 强烈推荐!</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -880,24 +1104,44 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6092</v>
+        <v>6094</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Find the local LLM that actually runs and performs best on your hardware. Ranked by real, recency-aw</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find the local LLM that actually runs and performs best on your hardware. Ranked by real, recency-aware benchmarks, not parameter count. One command, </t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>按硬件推荐能跑的本地模型, 选模型神器</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -921,17 +1165,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>The fastest local AI engine for Apple Silicon. 4.2x faster than Ollama, 0.08s cached TTFT, 100% tool</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>The fastest local AI engine for Apple Silicon. 4.2x faster than Ollama, 0.08s cached TTFT, 100% tool calling. 17 tool parsers, prompt cache, reasoning</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>本地跑模型相关, 配合你的DeepSeek部署经验</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -955,17 +1219,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>RamaLama is an open-source developer tool that simplifies the local serving of AI models from any so</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>RamaLama is an open-source developer tool that simplifies the local serving of AI models from any source and facilitates their use for inference in pr</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>容器化一键跑本地模型, 免配置环境</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -989,17 +1273,37 @@
           <t>Swift</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>A native macOS AI chat app powered by MLX. 100% local inference on Apple Silicon, no cloud required.</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>A native macOS AI chat app powered by MLX. 100% local inference on Apple Silicon, no cloud required. Built with ShipSwift.</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>本地跑模型相关, 配合你的DeepSeek部署经验</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1016,24 +1320,44 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Local AI app and inference engine for agents. Run open-weight LLMs locally — private, 100% offline o</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Local AI app and inference engine for agents. Run open-weight LLMs locally — private, 100% offline on your computer.</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>本地跑模型相关, 配合你的DeepSeek部署经验</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1057,17 +1381,37 @@
           <t>Kotlin</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Android 17 local LLM prototype with Jetpack Compose and ONNX Runtime for offline AI inference experi</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Android 17 local LLM prototype with Jetpack Compose and ONNX Runtime for offline AI inference experiments.</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>本地跑模型相关, 配合你的DeepSeek部署经验</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1091,17 +1435,37 @@
           <t>C#</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>AI Productivity Tool - Free and open source, improve user productivity, and protect privacy and data</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Productivity Tool - Free and open source, improve user productivity, and protect privacy and data security. Including but not limited to: built-in </t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>本地跑模型相关, 配合你的DeepSeek部署经验</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1116,6 +1480,10 @@
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1139,17 +1507,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Apache Superset is a Data Visualization and Data Exploration Platform</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>企业级数据可视化平台, 功能全但部署较重</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1166,24 +1554,44 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>28719</v>
+        <v>28720</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Make Your Company Data Driven. Connect to any data source, easily visualize, dashboard and share you</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Make Your Company Data Driven. Connect to any data source, easily visualize, dashboard and share your data.</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>SQL查询+看板, 轻量版Superset</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1207,17 +1615,37 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Interactive Data Visualization in the browser, from  Python</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>交互式浏览器可视化, 配合数据分析很实用</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1241,17 +1669,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Statistical data visualization in Python</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>统计绘图必备库, 论文图表神器, 必学</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1268,24 +1716,44 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>13852</v>
+        <v>13853</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>C++</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Open3D: A Modern Library for 3D Data Processing</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>3D点云处理, 研究方向才需要</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1302,24 +1770,44 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>11225</v>
+        <v>11227</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Visualize, query, and stream to train on multimodal robotics data.</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>多模态/机器人数据可视化, 偏科研</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1343,17 +1831,37 @@
           <t>Rust</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>A data visualization and analytics component, especially well-suited for large and/or streaming data</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>A data visualization and analytics component, especially well-suited for large and/or streaming datasets.</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>可视化工具, 按需学习</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1377,17 +1885,37 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Browser-based frontend to gdb (gnu debugger). Add breakpoints, view the stack, visualize data struct</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Browser-based frontend to gdb (gnu debugger). Add breakpoints, view the stack, visualize data structures, and more in C, C++, Go, Rust, and Fortran. R</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>可视化工具, 按需学习</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1402,6 +1930,10 @@
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1425,17 +1957,37 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">:cancer: Interactive Particle / Nest System With JavaScript and Canvas, no jQuery. </t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>网页粒子背景, 和你的粒子项目同源, 可借鉴</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1459,17 +2011,37 @@
           <t>Kotlin</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Celebrate more with this lightweight confetti particle system 🎊</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Android彩纸粒子特效, 移动端</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1493,17 +2065,37 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>a particle system designer using HTML5 Canvas</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Canvas粒子系统设计器, 学习粒子思路</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1527,17 +2119,37 @@
           <t>PHP</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>:zap: A wordpress plugin of canvas-nest.js (Interactive Particle / Nest System With JavaScript and C</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>:zap: A wordpress plugin of canvas-nest.js (Interactive Particle / Nest System With JavaScript and Canvas, Do not Depends on jQuery)</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>与你的粒子项目同源, 可借鉴实现思路</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1561,17 +2173,37 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Gravity Simulation (Galaxy Birth) in real time, N-Body and 1-Body</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>N体引力模拟(星系诞生), 物理粒子</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1595,17 +2227,37 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>A single-page HTML canvas/JavaScript implementation of the Primordial Particle System by Thomas Schm</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>A single-page HTML canvas/JavaScript implementation of the Primordial Particle System by Thomas Schmickl &amp; Martin Stefanec of Graz University, Austria</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>原始粒子系统, 艺术向</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -1629,17 +2281,37 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>A simple particle system using html5 canvas</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>与你的粒子项目同源, 可借鉴实现思路</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -1663,17 +2335,37 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>A simple lightweight 2D particle system using Canvas.</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>与你的粒子项目同源, 可借鉴实现思路</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1688,6 +2380,10 @@
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -1711,17 +2407,37 @@
           <t>R</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>An R-tool for comprehensive science mapping analysis. A package for quantitative research in sciento</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>An R-tool for comprehensive science mapping analysis. A package for quantitative research in scientometrics and bibliometrics.</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -1745,17 +2461,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>A bibliometrics tool for publication metadata (pubmed, arxiv, medrxiv, biorxiv, chemrxiv) and citati</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>A bibliometrics tool for publication metadata (pubmed, arxiv, medrxiv, biorxiv, chemrxiv) and citation analyses</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -1779,17 +2515,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Python-based API-Wrapper to access Scopus</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -1813,17 +2569,37 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Wikidata-based scholarly profiles </t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -1847,17 +2623,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>LitStudy: Using the power of Python to automate scientific literature analysis from the comfort of a</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>LitStudy: Using the power of Python to automate scientific literature analysis from the comfort of a Jupyter notebook</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -1874,24 +2670,44 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>A Bibliometric and Scientometric Python Library Powered with Artificial Intelligence Tools</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -1915,17 +2731,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>A curated collection of resources on scholarly data analysis ranging from datasets, papers, and code</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>A curated collection of resources on scholarly data analysis ranging from datasets, papers, and code about bibliometrics, citation analysis, and other</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -1949,17 +2785,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>A Python library for doing bibliometric and network analysis in science and health policy research</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>学术方向相关, 可与CiteSpace工作流结合</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1974,6 +2830,10 @@
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -1990,24 +2850,44 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>37154</v>
+        <v>37182</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>★★★★</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Build your personal knowledge base with Trilium Notes</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2024,24 +2904,44 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>10217</v>
+        <v>10241</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Self-organizing AI second brain for Obsidian + Claude Code. Drop any source and Claude reads, links,</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Self-organizing AI second brain for Obsidian + Claude Code. Drop any source and Claude reads, links, and files it into one connected knowledge graph o</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -2065,17 +2965,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>This is my personal knowledge-base. Here you'll find code-snippets, technical documentation, and com</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>This is my personal knowledge-base. Here you'll find code-snippets, technical documentation, and command reference for various tools, and technologies</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2099,17 +3019,37 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Mirix is a multi-agent personal assistant designed to track on-screen activities and answer user que</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Mirix is a multi-agent personal assistant designed to track on-screen activities and answer user questions intelligently. By capturing real-time visua</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -2126,24 +3066,44 @@
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>3299</v>
+        <v>3301</v>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>A personal knowledge base that builds and maintains itself. Drop in sources — Claude (or Codex/Gemin</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>A personal knowledge base that builds and maintains itself. Drop in sources — Claude (or Codex/Gemini) reads them, extracts knowledge, and maintains a</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2167,17 +3127,37 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Build your personal knowledge base with TriliumNext Notes</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2194,24 +3174,44 @@
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Self-hosted, semantically-connected personal knowledge base</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2235,77 +3235,104 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>LLM-maintained personal knowledge base for Obsidian. Based on Andrej Karpathy's LLM Wiki pattern.</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>待验证</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>个人知识管理, 数据积累方向实用</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>待验证</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>【粒子系统】</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>粒子系统</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>★本地成果: 二次元粒子系统 (Hermes定制)</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Python/JS</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>粒子汇聚成二次元角色(全彩/简笔画/线条模式, 8万粒子, 60fps)</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>本地已完成, 手机+PC双端可用</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
         <is>
           <t>已复现</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr"/>
+      <c r="L56" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A47:H47"/>
+  <mergeCells count="6">
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A47:L47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2317,11 +3344,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>开源项目汇总表 - 使用说明</t>
         </is>
@@ -2330,45 +3357,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 状态列含义:</t>
+          <t>1. 实用度: ★1-5, 越高越值得花时间</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   已复现 = 已在本地运行/复现成功</t>
+          <t>2. 复现难度: 低(几小时)/中(1-2天)/高(一周+)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   未复现 = 尝试过但未成功</t>
+          <t>3. 状态列: 已复现=本地跑通 / 未复现=尝试失败 / 待验证=未尝试</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   待验证 = 尚未在本地尝试</t>
+          <t>4. 筛选建议: 先看实用度4星以上 + 难度低/中的项目</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5. 本表每周一由 cron 自动更新 (新增项目自动追加)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2. 本表由定期脚本自动更新 (每周), 新增项目自动追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3. 最近更新: 2026-08-02 00:37</t>
+          <t>6. 想复现哪个项目, 告诉 Hermes 即可自动尝试</t>
         </is>
       </c>
     </row>
